--- a/Res_ConvLSTM/DroughtDataset_model_testing_1753960290_individual_h_6.xlsx
+++ b/Res_ConvLSTM/DroughtDataset_model_testing_1753960290_individual_h_6.xlsx
@@ -658,7 +658,7 @@
         <v>0.008454177761639635</v>
       </c>
       <c r="C2" t="n">
-        <v>37877868</v>
+        <v>6312978</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -679,49 +679,49 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>37877868</v>
+        <v>6312978</v>
       </c>
       <c r="K2" t="n">
-        <v>27498479</v>
+        <v>4267041</v>
       </c>
       <c r="L2" t="n">
-        <v>15974226</v>
+        <v>2167546</v>
       </c>
       <c r="M2" t="n">
-        <v>4036765</v>
+        <v>492977</v>
       </c>
       <c r="N2" t="n">
-        <v>209027</v>
+        <v>13633</v>
       </c>
       <c r="O2" t="n">
-        <v>2392009</v>
+        <v>294330</v>
       </c>
       <c r="P2" t="n">
-        <v>932502</v>
+        <v>114927</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.9999750256538391</v>
+        <v>0.9999253749847412</v>
       </c>
       <c r="R2" t="n">
-        <v>0.9030280113220215</v>
+        <v>0.8205958604812622</v>
       </c>
       <c r="S2" t="n">
-        <v>0.8068362474441528</v>
+        <v>0.6685636043548584</v>
       </c>
       <c r="T2" t="n">
-        <v>0.7584234476089478</v>
+        <v>0.5727402567863464</v>
       </c>
       <c r="U2" t="n">
-        <v>0.4499210119247437</v>
+        <v>0.1413244009017944</v>
       </c>
       <c r="V2" t="n">
-        <v>0.7996930480003357</v>
+        <v>0.6325610280036926</v>
       </c>
       <c r="W2" t="n">
-        <v>0.8711259365081787</v>
+        <v>0.7579537034034729</v>
       </c>
       <c r="X2" t="n">
-        <v>37877868</v>
+        <v>6312978</v>
       </c>
       <c r="Y2" t="n">
         <v>0</v>
@@ -742,46 +742,46 @@
         <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>37877868</v>
+        <v>6312978</v>
       </c>
       <c r="AF2" t="n">
-        <v>28872412</v>
+        <v>4796855</v>
       </c>
       <c r="AG2" t="n">
-        <v>17836630</v>
+        <v>2983951</v>
       </c>
       <c r="AH2" t="n">
-        <v>4798928</v>
+        <v>801380</v>
       </c>
       <c r="AI2" t="n">
-        <v>353991</v>
+        <v>59049</v>
       </c>
       <c r="AJ2" t="n">
-        <v>2755108</v>
+        <v>459641</v>
       </c>
       <c r="AK2" t="n">
-        <v>1080323</v>
+        <v>180138</v>
       </c>
       <c r="AL2" t="n">
         <v>1</v>
       </c>
       <c r="AM2" t="n">
-        <v>0.9564692974090576</v>
+        <v>0.9560109972953796</v>
       </c>
       <c r="AN2" t="n">
-        <v>0.9113166332244873</v>
+        <v>0.9115679264068604</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.8581637144088745</v>
+        <v>0.8585426211357117</v>
       </c>
       <c r="AP2" t="n">
-        <v>0.6622001528739929</v>
+        <v>0.6615541577339172</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0.9020119309425354</v>
+        <v>0.9020492434501648</v>
       </c>
       <c r="AR2" t="n">
-        <v>0.9314349889755249</v>
+        <v>0.9314607977867126</v>
       </c>
     </row>
     <row r="3">
@@ -792,130 +792,130 @@
         <v>0.002027047184025982</v>
       </c>
       <c r="C3" t="n">
-        <v>696</v>
+        <v>331</v>
       </c>
       <c r="D3" t="n">
-        <v>27498479</v>
+        <v>4267041</v>
       </c>
       <c r="E3" t="n">
-        <v>2602468</v>
+        <v>721996</v>
       </c>
       <c r="F3" t="n">
-        <v>43710</v>
+        <v>17899</v>
       </c>
       <c r="G3" t="n">
-        <v>4385</v>
+        <v>1298</v>
       </c>
       <c r="H3" t="n">
-        <v>2326</v>
+        <v>1018</v>
       </c>
       <c r="I3" t="n">
-        <v>84</v>
+        <v>25</v>
       </c>
       <c r="J3" t="n">
-        <v>60098787</v>
+        <v>10016151</v>
       </c>
       <c r="K3" t="n">
-        <v>64872517</v>
+        <v>10387103</v>
       </c>
       <c r="L3" t="n">
-        <v>74552794</v>
+        <v>11975794</v>
       </c>
       <c r="M3" t="n">
-        <v>91095462</v>
+        <v>15026810</v>
       </c>
       <c r="N3" t="n">
-        <v>97187050</v>
+        <v>16157423</v>
       </c>
       <c r="O3" t="n">
-        <v>94322645</v>
+        <v>15648692</v>
       </c>
       <c r="P3" t="n">
-        <v>96679621</v>
+        <v>16099459</v>
       </c>
       <c r="Q3" t="n">
         <v>1</v>
       </c>
       <c r="R3" t="n">
-        <v>0.9119907021522522</v>
+        <v>0.8517714142799377</v>
       </c>
       <c r="S3" t="n">
-        <v>0.8149935007095337</v>
+        <v>0.6609867215156555</v>
       </c>
       <c r="T3" t="n">
-        <v>0.7213237285614014</v>
+        <v>0.5272295475006104</v>
       </c>
       <c r="U3" t="n">
-        <v>0.39071124792099</v>
+        <v>0.1525899916887283</v>
       </c>
       <c r="V3" t="n">
-        <v>0.7827754020690918</v>
+        <v>0.5771867036819458</v>
       </c>
       <c r="W3" t="n">
-        <v>0.8038637042045593</v>
+        <v>0.5941222310066223</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>28872412</v>
+        <v>4796855</v>
       </c>
       <c r="Z3" t="n">
-        <v>1187392</v>
+        <v>197460</v>
       </c>
       <c r="AA3" t="n">
-        <v>51135</v>
+        <v>8429</v>
       </c>
       <c r="AB3" t="n">
-        <v>40793</v>
+        <v>6823</v>
       </c>
       <c r="AC3" t="n">
-        <v>236</v>
+        <v>11</v>
       </c>
       <c r="AD3" t="n">
-        <v>180</v>
+        <v>30</v>
       </c>
       <c r="AE3" t="n">
-        <v>60099732</v>
+        <v>10016622</v>
       </c>
       <c r="AF3" t="n">
-        <v>66511414</v>
+        <v>11099274</v>
       </c>
       <c r="AG3" t="n">
-        <v>76641422</v>
+        <v>12760866</v>
       </c>
       <c r="AH3" t="n">
-        <v>91588110</v>
+        <v>15262528</v>
       </c>
       <c r="AI3" t="n">
-        <v>97262032</v>
+        <v>16210047</v>
       </c>
       <c r="AJ3" t="n">
-        <v>94622500</v>
+        <v>15769750</v>
       </c>
       <c r="AK3" t="n">
-        <v>96738050</v>
+        <v>16122905</v>
       </c>
       <c r="AL3" t="n">
         <v>1</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.9575573801994324</v>
+        <v>0.9575310349464417</v>
       </c>
       <c r="AN3" t="n">
-        <v>0.9100120067596436</v>
+        <v>0.9099469780921936</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.8575135469436646</v>
+        <v>0.8570606708526611</v>
       </c>
       <c r="AP3" t="n">
-        <v>0.6616765260696411</v>
+        <v>0.660917341709137</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0.9015980958938599</v>
+        <v>0.9013646841049194</v>
       </c>
       <c r="AR3" t="n">
-        <v>0.9312928318977356</v>
+        <v>0.9312344789505005</v>
       </c>
     </row>
     <row r="4">
@@ -926,285 +926,285 @@
         <v>0.03199143872576704</v>
       </c>
       <c r="C4" t="n">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="D4" t="n">
-        <v>2788775</v>
+        <v>877253</v>
       </c>
       <c r="E4" t="n">
-        <v>15974226</v>
+        <v>2167546</v>
       </c>
       <c r="F4" t="n">
-        <v>751183</v>
+        <v>203363</v>
       </c>
       <c r="G4" t="n">
-        <v>28152</v>
+        <v>9590</v>
       </c>
       <c r="H4" t="n">
-        <v>53777</v>
+        <v>19660</v>
       </c>
       <c r="I4" t="n">
-        <v>4274</v>
+        <v>1802</v>
       </c>
       <c r="J4" t="n">
-        <v>945</v>
+        <v>471</v>
       </c>
       <c r="K4" t="n">
-        <v>2952935</v>
+        <v>932889</v>
       </c>
       <c r="L4" t="n">
-        <v>3824372</v>
+        <v>1074548</v>
       </c>
       <c r="M4" t="n">
-        <v>1285809</v>
+        <v>367757</v>
       </c>
       <c r="N4" t="n">
-        <v>255559</v>
+        <v>82833</v>
       </c>
       <c r="O4" t="n">
-        <v>599150</v>
+        <v>170969</v>
       </c>
       <c r="P4" t="n">
-        <v>137954</v>
+        <v>36701</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.9999875426292419</v>
+        <v>0.9999626874923706</v>
       </c>
       <c r="R4" t="n">
-        <v>0.9074872732162476</v>
+        <v>0.8358930349349976</v>
       </c>
       <c r="S4" t="n">
-        <v>0.8108943700790405</v>
+        <v>0.6647536158561707</v>
       </c>
       <c r="T4" t="n">
-        <v>0.7394084930419922</v>
+        <v>0.5490434169769287</v>
       </c>
       <c r="U4" t="n">
-        <v>0.4182309210300446</v>
+        <v>0.1467413008213043</v>
       </c>
       <c r="V4" t="n">
-        <v>0.7911437153816223</v>
+        <v>0.6036064624786377</v>
       </c>
       <c r="W4" t="n">
-        <v>0.8361442685127258</v>
+        <v>0.6661121845245361</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>1226769</v>
+        <v>206052</v>
       </c>
       <c r="Z4" t="n">
-        <v>17836630</v>
+        <v>2983951</v>
       </c>
       <c r="AA4" t="n">
-        <v>496804</v>
+        <v>82537</v>
       </c>
       <c r="AB4" t="n">
-        <v>32965</v>
+        <v>5520</v>
       </c>
       <c r="AC4" t="n">
-        <v>6858</v>
+        <v>1130</v>
       </c>
       <c r="AD4" t="n">
-        <v>408</v>
+        <v>68</v>
       </c>
       <c r="AE4" t="n">
         <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>1314038</v>
+        <v>220718</v>
       </c>
       <c r="AG4" t="n">
-        <v>1735744</v>
+        <v>289476</v>
       </c>
       <c r="AH4" t="n">
-        <v>793161</v>
+        <v>132039</v>
       </c>
       <c r="AI4" t="n">
-        <v>180577</v>
+        <v>30209</v>
       </c>
       <c r="AJ4" t="n">
-        <v>299295</v>
+        <v>49911</v>
       </c>
       <c r="AK4" t="n">
-        <v>79525</v>
+        <v>13255</v>
       </c>
       <c r="AL4" t="n">
         <v>1</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.9570130109786987</v>
+        <v>0.9567704200744629</v>
       </c>
       <c r="AN4" t="n">
-        <v>0.910663902759552</v>
+        <v>0.9107567667961121</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.85783851146698</v>
+        <v>0.8578009605407715</v>
       </c>
       <c r="AP4" t="n">
-        <v>0.6619382500648499</v>
+        <v>0.6612355709075928</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0.9018049240112305</v>
+        <v>0.9017068147659302</v>
       </c>
       <c r="AR4" t="n">
-        <v>0.9313638806343079</v>
+        <v>0.9313476085662842</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr"/>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="D5" t="n">
-        <v>105712</v>
+        <v>38424</v>
       </c>
       <c r="E5" t="n">
-        <v>1045768</v>
+        <v>295964</v>
       </c>
       <c r="F5" t="n">
-        <v>4036765</v>
+        <v>492977</v>
       </c>
       <c r="G5" t="n">
-        <v>96901</v>
+        <v>26546</v>
       </c>
       <c r="H5" t="n">
-        <v>289634</v>
+        <v>73326</v>
       </c>
       <c r="I5" t="n">
-        <v>21527</v>
+        <v>7779</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>2653669</v>
+        <v>742567</v>
       </c>
       <c r="L5" t="n">
-        <v>3626208</v>
+        <v>1111712</v>
       </c>
       <c r="M5" t="n">
-        <v>1559564</v>
+        <v>442056</v>
       </c>
       <c r="N5" t="n">
-        <v>325964</v>
+        <v>75711</v>
       </c>
       <c r="O5" t="n">
-        <v>663796</v>
+        <v>215609</v>
       </c>
       <c r="P5" t="n">
-        <v>227523</v>
+        <v>78513</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.9999903440475464</v>
+        <v>0.9999711513519287</v>
       </c>
       <c r="R5" t="n">
-        <v>0.9427766799926758</v>
+        <v>0.8973976373672485</v>
       </c>
       <c r="S5" t="n">
-        <v>0.9239562749862671</v>
+        <v>0.8661167621612549</v>
       </c>
       <c r="T5" t="n">
-        <v>0.970958948135376</v>
+        <v>0.9504082798957825</v>
       </c>
       <c r="U5" t="n">
-        <v>0.9940647482872009</v>
+        <v>0.9902909994125366</v>
       </c>
       <c r="V5" t="n">
-        <v>0.9871098399162292</v>
+        <v>0.9763265252113342</v>
       </c>
       <c r="W5" t="n">
-        <v>0.9962697625160217</v>
+        <v>0.9929444789886475</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>48155</v>
+        <v>8093</v>
       </c>
       <c r="Z5" t="n">
-        <v>510890</v>
+        <v>85757</v>
       </c>
       <c r="AA5" t="n">
-        <v>4798928</v>
+        <v>801380</v>
       </c>
       <c r="AB5" t="n">
-        <v>59714</v>
+        <v>9985</v>
       </c>
       <c r="AC5" t="n">
-        <v>174844</v>
+        <v>29185</v>
       </c>
       <c r="AD5" t="n">
-        <v>3798</v>
+        <v>633</v>
       </c>
       <c r="AE5" t="n">
         <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>1279736</v>
+        <v>212753</v>
       </c>
       <c r="AG5" t="n">
-        <v>1763804</v>
+        <v>295307</v>
       </c>
       <c r="AH5" t="n">
-        <v>797401</v>
+        <v>133653</v>
       </c>
       <c r="AI5" t="n">
-        <v>181000</v>
+        <v>30295</v>
       </c>
       <c r="AJ5" t="n">
-        <v>300697</v>
+        <v>50298</v>
       </c>
       <c r="AK5" t="n">
-        <v>79702</v>
+        <v>13302</v>
       </c>
       <c r="AL5" t="n">
         <v>1</v>
       </c>
       <c r="AM5" t="n">
-        <v>0.9735268950462341</v>
+        <v>0.9734548926353455</v>
       </c>
       <c r="AN5" t="n">
-        <v>0.9642821550369263</v>
+        <v>0.9641887545585632</v>
       </c>
       <c r="AO5" t="n">
-        <v>0.9837660789489746</v>
+        <v>0.9837294220924377</v>
       </c>
       <c r="AP5" t="n">
-        <v>0.9963095784187317</v>
+        <v>0.9962948560714722</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0.9938762187957764</v>
+        <v>0.9938633441925049</v>
       </c>
       <c r="AR5" t="n">
-        <v>0.998374879360199</v>
+        <v>0.9983736872673035</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr"/>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>52</v>
+        <v>15</v>
       </c>
       <c r="D6" t="n">
-        <v>56549</v>
+        <v>15805</v>
       </c>
       <c r="E6" t="n">
-        <v>96712</v>
+        <v>20352</v>
       </c>
       <c r="F6" t="n">
-        <v>116377</v>
+        <v>27956</v>
       </c>
       <c r="G6" t="n">
-        <v>209027</v>
+        <v>13633</v>
       </c>
       <c r="H6" t="n">
-        <v>52064</v>
+        <v>10520</v>
       </c>
       <c r="I6" t="n">
-        <v>4210</v>
+        <v>1063</v>
       </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
@@ -1224,22 +1224,22 @@
         <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>38779</v>
+        <v>6517</v>
       </c>
       <c r="Z6" t="n">
-        <v>32116</v>
+        <v>5368</v>
       </c>
       <c r="AA6" t="n">
-        <v>65335</v>
+        <v>10940</v>
       </c>
       <c r="AB6" t="n">
-        <v>353991</v>
+        <v>59049</v>
       </c>
       <c r="AC6" t="n">
-        <v>41884</v>
+        <v>6989</v>
       </c>
       <c r="AD6" t="n">
-        <v>2886</v>
+        <v>481</v>
       </c>
       <c r="AE6" t="inlineStr"/>
       <c r="AF6" t="inlineStr"/>
@@ -1260,25 +1260,25 @@
       <c r="A7" t="inlineStr"/>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
-        <v>56</v>
+        <v>43</v>
       </c>
       <c r="D7" t="n">
-        <v>1762</v>
+        <v>1361</v>
       </c>
       <c r="E7" t="n">
-        <v>75149</v>
+        <v>34034</v>
       </c>
       <c r="F7" t="n">
-        <v>359755</v>
+        <v>111870</v>
       </c>
       <c r="G7" t="n">
-        <v>119215</v>
+        <v>42269</v>
       </c>
       <c r="H7" t="n">
-        <v>2392009</v>
+        <v>294330</v>
       </c>
       <c r="I7" t="n">
-        <v>107859</v>
+        <v>26032</v>
       </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
@@ -1298,22 +1298,22 @@
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>167</v>
+        <v>28</v>
       </c>
       <c r="Z7" t="n">
-        <v>4860</v>
+        <v>810</v>
       </c>
       <c r="AA7" t="n">
-        <v>177905</v>
+        <v>29802</v>
       </c>
       <c r="AB7" t="n">
-        <v>45512</v>
+        <v>7615</v>
       </c>
       <c r="AC7" t="n">
-        <v>2755108</v>
+        <v>459641</v>
       </c>
       <c r="AD7" t="n">
-        <v>72253</v>
+        <v>12043</v>
       </c>
       <c r="AE7" t="inlineStr"/>
       <c r="AF7" t="inlineStr"/>
@@ -1334,25 +1334,25 @@
       <c r="A8" t="inlineStr"/>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>72</v>
+        <v>21</v>
       </c>
       <c r="D8" t="n">
-        <v>137</v>
+        <v>46</v>
       </c>
       <c r="E8" t="n">
-        <v>4275</v>
+        <v>2202</v>
       </c>
       <c r="F8" t="n">
-        <v>14784</v>
+        <v>6669</v>
       </c>
       <c r="G8" t="n">
-        <v>6906</v>
+        <v>3130</v>
       </c>
       <c r="H8" t="n">
-        <v>201349</v>
+        <v>66445</v>
       </c>
       <c r="I8" t="n">
-        <v>932502</v>
+        <v>114927</v>
       </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
@@ -1372,22 +1372,22 @@
         <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>168</v>
+        <v>28</v>
       </c>
       <c r="Z8" t="n">
-        <v>486</v>
+        <v>81</v>
       </c>
       <c r="AA8" t="n">
-        <v>1982</v>
+        <v>331</v>
       </c>
       <c r="AB8" t="n">
-        <v>1593</v>
+        <v>266</v>
       </c>
       <c r="AC8" t="n">
-        <v>75473</v>
+        <v>12596</v>
       </c>
       <c r="AD8" t="n">
-        <v>1080323</v>
+        <v>180138</v>
       </c>
       <c r="AE8" t="inlineStr"/>
       <c r="AF8" t="inlineStr"/>
